--- a/old_bom.xlsx
+++ b/old_bom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView/>
+    <workbookView windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="old_bom" sheetId="1" r:id="rId1"/>
@@ -32,1515 +32,1515 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="604">
   <si>
+    <t>Designator</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Designator</t>
-  </si>
-  <si>
     <t>Footprint</t>
   </si>
   <si>
+    <t>VALUE</t>
+  </si>
+  <si>
     <t>K3 No.</t>
   </si>
   <si>
-    <t>VALUE</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
+    <t>C1, C5, C6, C16, C33, C36, C39, C65, C66, C72, C75, C86, C92, C106, C149, C152</t>
+  </si>
+  <si>
     <t>CAP,CER,100nF,10%,50V,X7R,0603</t>
   </si>
   <si>
-    <t>C1, C5, C6, C16, C33, C36, C39, C65, C66, C72, C75, C86, C92, C106, C149, C152</t>
-  </si>
-  <si>
     <t>CAPC-0603</t>
   </si>
   <si>
+    <t>100nF</t>
+  </si>
+  <si>
     <t>1.1.1.01.02.025-GJ</t>
   </si>
   <si>
-    <t>100nF</t>
+    <t>C2, C8, C12, C15, C30, C97, C112, C113</t>
   </si>
   <si>
     <t>CAP,CER,1nF,5%,50V,C0G,0603</t>
   </si>
   <si>
-    <t>C2, C8, C12, C15, C30, C97, C112, C113</t>
+    <t>1nF</t>
   </si>
   <si>
     <t>1.1.1.01.02.003</t>
   </si>
   <si>
-    <t>1nF</t>
+    <t>C3, C4, C7, C13, C23, C32, C54, C61, C130</t>
   </si>
   <si>
     <t>CAP,CER,10nF,10%,50V,X7R,0603</t>
   </si>
   <si>
-    <t>C3, C4, C7, C13, C23, C32, C54, C61, C130</t>
+    <t>10nF</t>
   </si>
   <si>
     <t>1.1.1.01.02.002</t>
   </si>
   <si>
-    <t>10nF</t>
+    <t>C9, C26, C27, C28, C41, C43, C47, C48, C49, C50, C52, C77, C78, C80, C91, C100, C102, C103, C105, C107, C111, C116, C117, C118, C119, C120, C121, C122, C123, C124, C125, C128, C129, C155, C157, C159, C161, C162, C165, C195, C198, C200, C310, C312, C313</t>
   </si>
   <si>
     <t>CAP,CER,100nF,10%,16V,X7R,0402</t>
   </si>
   <si>
-    <t>C9, C26, C27, C28, C41, C43, C47, C48, C49, C50, C52, C77, C78, C80, C91, C100, C102, C103, C105, C107, C111, C116, C117, C118, C119, C120, C121, C122, C123, C124, C125, C128, C129, C155, C157, C159, C161, C162, C165, C195, C198, C200, C310, C312, C313</t>
-  </si>
-  <si>
     <t>CAPC-0402</t>
   </si>
   <si>
     <t>1.1.1.01.02.168</t>
   </si>
   <si>
+    <t>C10, C18, C35, C151</t>
+  </si>
+  <si>
     <t>CAP,ELEC,47uF,20%,50V,D6*L7</t>
   </si>
   <si>
-    <t>C10, C18, C35, C151</t>
-  </si>
-  <si>
     <t>CAPAE-6*6</t>
   </si>
   <si>
+    <t>47uF</t>
+  </si>
+  <si>
     <t>1.1.1.01.02.070</t>
   </si>
   <si>
-    <t>47uF</t>
+    <t>C11, C87, C88, C89</t>
   </si>
   <si>
     <t>CAP,CER,4.7uF,10%,50V,X7R,1206</t>
   </si>
   <si>
-    <t>C11, C87, C88, C89</t>
-  </si>
-  <si>
     <t>CAPC-1206</t>
   </si>
   <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
     <t>1.1.1.01.02.059</t>
   </si>
   <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
     <t>C14</t>
   </si>
   <si>
     <t>DNP</t>
   </si>
   <si>
+    <t>C17</t>
+  </si>
+  <si>
     <t>CAP,CER,100pF,10%,16V,X7R,0603</t>
   </si>
   <si>
-    <t>C17</t>
+    <t>100pF</t>
   </si>
   <si>
     <t>1.1.1.01.02.035GJ</t>
   </si>
   <si>
-    <t>100pF</t>
+    <t>C19</t>
   </si>
   <si>
     <t>CAP,CER,470nF,10%,16V,X7R,0603</t>
   </si>
   <si>
-    <t>C19</t>
+    <t>470nF</t>
   </si>
   <si>
     <t>1.1.1.01.02.172</t>
   </si>
   <si>
-    <t>470nF</t>
-  </si>
-  <si>
     <t>C20</t>
   </si>
   <si>
+    <t>C21</t>
+  </si>
+  <si>
     <t>CAP,CER,1uF,10%,50V,X7R,0603</t>
   </si>
   <si>
-    <t>C21</t>
+    <t>1uF</t>
   </si>
   <si>
     <t>1.1.1.01.02.124</t>
   </si>
   <si>
-    <t>1uF</t>
-  </si>
-  <si>
     <t>C24, C25, C85</t>
   </si>
   <si>
+    <t>C29, C101, C104, C126, C127, C158, C160, C168, C199</t>
+  </si>
+  <si>
     <t>CAP,CER,2.2uF,10%,16V,X7R,0402</t>
   </si>
   <si>
-    <t>C29, C101, C104, C126, C127, C158, C160, C168, C199</t>
+    <t>2.2uF</t>
   </si>
   <si>
     <t>1.1.1.01.02.187</t>
   </si>
   <si>
-    <t>2.2uF</t>
+    <t>C31, C45, C60, C98</t>
   </si>
   <si>
     <t>CAP,CER,10nF,10%,100V,X7R,0805</t>
   </si>
   <si>
-    <t>C31, C45, C60, C98</t>
-  </si>
-  <si>
     <t>CAPC-0805</t>
   </si>
   <si>
     <t>1.1.1.01.02.048-GJ</t>
   </si>
   <si>
+    <t>C34</t>
+  </si>
+  <si>
     <t>CAP,CER,22pF,5%,50V,NPO,0402</t>
   </si>
   <si>
-    <t>C34</t>
+    <t>22pF</t>
   </si>
   <si>
     <t>1.1.1.01.02.130</t>
   </si>
   <si>
-    <t>22pF</t>
+    <t>C37, C38, C53, C79, C90, C93, C94, C95</t>
   </si>
   <si>
     <t>CAP,CER,10uF,10%,50V,X7R,1206</t>
   </si>
   <si>
-    <t>C37, C38, C53, C79, C90, C93, C94, C95</t>
+    <t>10uF</t>
   </si>
   <si>
     <t>1.1.1.01.02.171</t>
   </si>
   <si>
-    <t>10uF</t>
+    <t>C40</t>
   </si>
   <si>
     <t>CAP CER,1uF,10%,16V,X5R,0402</t>
   </si>
   <si>
-    <t>C40</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.139</t>
   </si>
   <si>
+    <t>C42</t>
+  </si>
+  <si>
     <t>CAP,CER,10uF,20%,6.3V,X5R,0402</t>
   </si>
   <si>
-    <t>C42</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.204</t>
   </si>
   <si>
+    <t>C44, C46, C51</t>
+  </si>
+  <si>
     <t>CAP,CER,1uF,10%,10V,X5R,0402</t>
   </si>
   <si>
-    <t>C44, C46, C51</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.169</t>
   </si>
   <si>
+    <t>C55, C58</t>
+  </si>
+  <si>
     <t>CAP CER,100pF,5%,100V,COG,0603</t>
   </si>
   <si>
-    <t>C55, C58</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.115</t>
   </si>
   <si>
+    <t>C56</t>
+  </si>
+  <si>
     <t>CAP,CER,4.7nF,10%,50V,X7R,0603</t>
   </si>
   <si>
-    <t>C56</t>
+    <t>4.7nF</t>
   </si>
   <si>
     <t>1.1.1.01.02.027</t>
   </si>
   <si>
-    <t>4.7nF</t>
-  </si>
-  <si>
     <t>C57, C59, C133</t>
   </si>
   <si>
+    <t>C62, C63, C64</t>
+  </si>
+  <si>
     <t>CAP,CER,100nF,10%,100V,X7R,0805</t>
   </si>
   <si>
-    <t>C62, C63, C64</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.014-SX</t>
   </si>
   <si>
+    <t>C67</t>
+  </si>
+  <si>
     <t>CAP,ELEC,220uF,20%,50V,D10*L10</t>
   </si>
   <si>
-    <t>C67</t>
-  </si>
-  <si>
     <t>CAPAE-10*10</t>
   </si>
   <si>
+    <t>220uF</t>
+  </si>
+  <si>
     <t>1.6.1.01.003.004</t>
   </si>
   <si>
-    <t>220uF</t>
+    <t>C68, C69, C70, C71, C74, C2104</t>
   </si>
   <si>
     <t>CAP,CER,10uF,20%,10V,X5R,0603</t>
   </si>
   <si>
-    <t>C68, C69, C70, C71, C74, C2104</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.164</t>
   </si>
   <si>
+    <t>C76</t>
+  </si>
+  <si>
     <t>CAP,CER,22uF,10%,25V,X7R,0805</t>
   </si>
   <si>
-    <t>C76</t>
+    <t>22uF</t>
   </si>
   <si>
     <t>1.1.1.01.02.154</t>
   </si>
   <si>
-    <t>22uF</t>
+    <t>C81, C82, C83, C84, C132</t>
   </si>
   <si>
     <t>CAP,CER,2.2uF,10%,50V,X7R,0805</t>
   </si>
   <si>
-    <t>C81, C82, C83, C84, C132</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.158</t>
   </si>
   <si>
+    <t>C96</t>
+  </si>
+  <si>
     <t>CAP,CER,1nF,10%,100V,X7R,0805</t>
   </si>
   <si>
-    <t>C96</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.053-SX</t>
   </si>
   <si>
+    <t>C99, C108, C109, C110, C2103, C2108, C2114, C2116, C2124, C2125</t>
+  </si>
+  <si>
     <t>cap,22.00uF,+/-20%,6.3V,X5R,C0603</t>
   </si>
   <si>
-    <t>C99, C108, C109, C110, C2103, C2108, C2114, C2116, C2124, C2125</t>
+    <t>C115, C136, C138, C139, C142, C145, C146, C147, C148, C150, C1002, C1003, C1004, C1005, C1008, C1009, C1010, C1011, C1100, C1103, C1104, C1105, C1108, C1201, C1202, C1203, C1204, C1205, C1206, C1300, C1400, C1401, C1402, C1500, C1701, C1702, C1703, C1704, C1800, C1801, C1802, C1903, C1904, C1905, C1906, C1908, C1910, C1911, C1912, C1913, C1914, C1919, C1920, C1921, C1922, C1923, C1924, C1925, C1926, C1927, C1928, C1929, C1930, C1931, C1932, C1934, C1935, C1936, C1937, C1938, C1939, C1940, C1941, C1945, C1946</t>
   </si>
   <si>
     <t>cap,100.00nF,+/-10%,10V,X5R,C0402, cap,100.00nF,+/-10%,6.3V,X5R,C0402, cap,100.00nF,+/-10%,16V,X5R,C0402</t>
   </si>
   <si>
-    <t>C115, C136, C138, C139, C142, C145, C146, C147, C148, C150, C1002, C1003, C1004, C1005, C1008, C1009, C1010, C1011, C1100, C1103, C1104, C1105, C1108, C1201, C1202, C1203, C1204, C1205, C1206, C1300, C1400, C1401, C1402, C1500, C1701, C1702, C1703, C1704, C1800, C1801, C1802, C1903, C1904, C1905, C1906, C1908, C1910, C1911, C1912, C1913, C1914, C1919, C1920, C1921, C1922, C1923, C1924, C1925, C1926, C1927, C1928, C1929, C1930, C1931, C1932, C1934, C1935, C1936, C1937, C1938, C1939, C1940, C1941, C1945, C1946</t>
-  </si>
-  <si>
     <t>C0402</t>
   </si>
   <si>
+    <t>C131, C140, C153</t>
+  </si>
+  <si>
     <t>CAP,CER,1nF,5%,50V,NPO,0402</t>
   </si>
   <si>
-    <t>C131, C140, C153</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.132</t>
   </si>
   <si>
+    <t>C134, C135</t>
+  </si>
+  <si>
     <t>CAP,CER,18pF,1%,25V,X5R,0603</t>
   </si>
   <si>
-    <t>C134, C135</t>
+    <t>18pF</t>
   </si>
   <si>
     <t>1.1.1.01.02.175</t>
   </si>
   <si>
-    <t>18pF</t>
+    <t>C137, C1915</t>
   </si>
   <si>
     <t>Did Not Place.</t>
   </si>
   <si>
-    <t>C137, C1915</t>
+    <t>C141, C1901</t>
   </si>
   <si>
     <t>cap,1.00uF,+/-10%,10V,X5R,C0402</t>
   </si>
   <si>
-    <t>C141, C1901</t>
+    <t>C143, C144, C169, C170, C1001, C1007, C1902, C1942</t>
   </si>
   <si>
     <t>cap,4.70uF,+/-10%,6.3V,X5R,C0402</t>
   </si>
   <si>
-    <t>C143, C144, C169, C170, C1001, C1007, C1902, C1942</t>
+    <t>C154, C156</t>
   </si>
   <si>
     <t>CAP,CER,4.7uF,10%,10V,X5R,0603</t>
   </si>
   <si>
-    <t>C154, C156</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.162</t>
   </si>
   <si>
+    <t>C163, C164, C166, C167</t>
+  </si>
+  <si>
     <t>CAP,CER,33nF,10%,50V,X7R,0402</t>
   </si>
   <si>
-    <t>C163, C164, C166, C167</t>
+    <t>33nF</t>
   </si>
   <si>
     <t>1.1.1.01.02.177</t>
   </si>
   <si>
-    <t>33nF</t>
+    <t>C281, C282, C2130, C2132</t>
   </si>
   <si>
     <t>CAP,CER,10pF,10%,16V,X7R,0402</t>
   </si>
   <si>
-    <t>C281, C282, C2130, C2132</t>
+    <t>10pF</t>
   </si>
   <si>
     <t>1.1.1.01.02.186</t>
   </si>
   <si>
-    <t>10pF</t>
+    <t>C283</t>
   </si>
   <si>
     <t>CAP,CER,10nF,10%,50V,X7R,0402</t>
   </si>
   <si>
-    <t>C283</t>
-  </si>
-  <si>
     <t>1.1.1.01.02.133</t>
   </si>
   <si>
+    <t>C1000, C1006</t>
+  </si>
+  <si>
     <t>cap,10.00uF,+/-10%,6.3V,X5R,C0603</t>
   </si>
   <si>
-    <t>C1000, C1006</t>
-  </si>
-  <si>
     <t>C0603</t>
   </si>
   <si>
+    <t>C1101, C1102</t>
+  </si>
+  <si>
     <t>cap,22.00pF,+/-2%,50V,C0G,C0402</t>
   </si>
   <si>
-    <t>C1101, C1102</t>
+    <t>C1200</t>
   </si>
   <si>
     <t>cap,4.70uF,+/-10%,10V,X5R,C0603</t>
   </si>
   <si>
-    <t>C1200</t>
+    <t>C1601, C1602</t>
   </si>
   <si>
     <t>CAP,CER,100nF,10%,6.3V,X5R,0201</t>
   </si>
   <si>
-    <t>C1601, C1602</t>
-  </si>
-  <si>
     <t>CAPC-0201</t>
   </si>
   <si>
     <t>1.1.1.01.02.159</t>
   </si>
   <si>
+    <t>C1700</t>
+  </si>
+  <si>
     <t>cap,100.00pF,+/-10%,50V,C0G,C0402</t>
   </si>
   <si>
-    <t>C1700</t>
+    <t>C1909, C1933</t>
   </si>
   <si>
     <t>cap,100.00nF,+/-10%,6.3V,X5R,C0402, cap,1.00nF,+/-10%,50V,X5R,C0402</t>
   </si>
   <si>
-    <t>C1909, C1933</t>
-  </si>
-  <si>
     <t>C1916, C1917, C1918</t>
   </si>
   <si>
+    <t>C2100, C2102, C2105, C2106, C2109, C2111, C2112, C2113, C2117, C2118, C2119, C2120, C2121, C2122, C2123, C2126, C2128, C4100</t>
+  </si>
+  <si>
     <t>cap,1.00uF,+/-10%,6.3V,X5R,C0402, cap,1.00uF,+/-10%,10V,X5R,C0402</t>
   </si>
   <si>
-    <t>C2100, C2102, C2105, C2106, C2109, C2111, C2112, C2113, C2117, C2118, C2119, C2120, C2121, C2122, C2123, C2126, C2128, C4100</t>
-  </si>
-  <si>
     <t>C2107, C2115</t>
   </si>
   <si>
+    <t>C2134, C2135, C2136, C2137, C2138</t>
+  </si>
+  <si>
     <t>cap,2.20uF,+/-10%,10V,X5R,C0402, cap,2.20uF,+/-10%,6.3V,X5R,C0402</t>
   </si>
   <si>
-    <t>C2134, C2135, C2136, C2137, C2138</t>
+    <t>C2139, C2141, C2143, C4102, C4103, C4105, C4107, C4108</t>
   </si>
   <si>
     <t>cap,100.00nF,+/-10%,25V,X5R,C0402, cap,100.00nF,+/-10%,6.3V,X5R,C0402, cap,100.00nF,+/-10%,10V,X5R,C0402</t>
   </si>
   <si>
-    <t>C2139, C2141, C2143, C4102, C4103, C4105, C4107, C4108</t>
-  </si>
-  <si>
     <t>C4101, C4104</t>
   </si>
   <si>
+    <t>D1, D12</t>
+  </si>
+  <si>
     <t>D,SCH,3A,100V,1,DO-214AA(HSMB)</t>
   </si>
   <si>
-    <t>D1, D12</t>
-  </si>
-  <si>
     <t>DIOC-5.2*2.6</t>
   </si>
   <si>
+    <t>SK310B</t>
+  </si>
+  <si>
     <t>1.1.1.01.03.053, 1.1.1.01.03.053A</t>
   </si>
   <si>
-    <t>SK310B</t>
+    <t>D2, D6, D7, D10, D11, D13</t>
   </si>
   <si>
     <t>D,SW,1,200mA,250V,1,SOD323/HIGH-VOLTAGE</t>
   </si>
   <si>
-    <t>D2, D6, D7, D10, D11, D13</t>
-  </si>
-  <si>
     <t>SOD-2.5*0.95</t>
   </si>
   <si>
+    <t>BAS21HT1G</t>
+  </si>
+  <si>
     <t>1.1.1.01.05.113</t>
   </si>
   <si>
-    <t>BAS21HT1G</t>
+    <t>D4</t>
   </si>
   <si>
     <t>D,SW,1,100mA,25V,1X2DFN-2P/HIGH-SPEED</t>
   </si>
   <si>
-    <t>D4</t>
-  </si>
-  <si>
     <t>X2DFN-2</t>
   </si>
   <si>
+    <t>SM0130MB</t>
+  </si>
+  <si>
     <t>1.1.1.01.03.112</t>
   </si>
   <si>
-    <t>SM0130MB</t>
+    <t>D5</t>
   </si>
   <si>
     <t>D,RECT,1A,1000V,1,SMA-W</t>
   </si>
   <si>
-    <t>D5</t>
+    <t>M7-01-W001</t>
   </si>
   <si>
     <t>1.1.1.01.03.013A</t>
   </si>
   <si>
-    <t>M7-01-W001</t>
+    <t>D8, D9</t>
   </si>
   <si>
     <t>D,RECT,3A,1000V,1，DO-214AB(SMC)</t>
   </si>
   <si>
-    <t>D8, D9</t>
-  </si>
-  <si>
     <t>DIOC-8*6</t>
   </si>
   <si>
+    <t>SS36</t>
+  </si>
+  <si>
     <t>1.1.1.01.03.102</t>
   </si>
   <si>
-    <t>SS36</t>
+    <t>DM, DM1</t>
   </si>
   <si>
     <t>Data Matrix Area</t>
   </si>
   <si>
-    <t>DM, DM1</t>
-  </si>
-  <si>
     <t>DM-10*10</t>
   </si>
   <si>
+    <t>FB1, FB2, FB3, FB4, FB5, FB7, FB10, FB11, FB12, FB13, FB14, FB15, FB16, FB17, FB18, FB19, FB20, FB23, FB24, FB25, FB26, FB27</t>
+  </si>
+  <si>
     <t>FBEAD,350mR,600R@100MHz,25%,400mA,0603, F BEAD,350mR,600R@100MHz,25%,400mA,0603</t>
   </si>
   <si>
-    <t>FB1, FB2, FB3, FB4, FB5, FB7, FB10, FB11, FB12, FB13, FB14, FB15, FB16, FB17, FB18, FB19, FB20, FB23, FB24, FB25, FB26, FB27</t>
-  </si>
-  <si>
     <t>FBC-0603</t>
   </si>
   <si>
+    <t>600R</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.015</t>
   </si>
   <si>
-    <t>600R</t>
+    <t>FB6, FB8, FB9, FB21, FB22</t>
   </si>
   <si>
     <t>F BEAD,1250mR,1kΩ@100MHz,25%,250mA,0402</t>
   </si>
   <si>
-    <t>FB6, FB8, FB9, FB21, FB22</t>
-  </si>
-  <si>
     <t>RESC-0402</t>
   </si>
   <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.101</t>
   </si>
   <si>
-    <t>1kΩ</t>
+    <t>FM1, FM2, FM3, FM4</t>
   </si>
   <si>
     <t>Fidicial Mark</t>
   </si>
   <si>
-    <t>FM1, FM2, FM3, FM4</t>
-  </si>
-  <si>
     <t>MARK-2L</t>
   </si>
   <si>
+    <t>J1</t>
+  </si>
+  <si>
     <t>CON,HSD,4-PIN</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
     <t>D4S10E-40MA5</t>
   </si>
   <si>
+    <t>1107042500（D4S11M-40MA5-D）</t>
+  </si>
+  <si>
     <t>1.1.1.02.14.148</t>
   </si>
   <si>
-    <t>1107042500（D4S11M-40MA5-D）</t>
+    <t>J2</t>
   </si>
   <si>
     <t>CON FPC,60P,1R,0.5MM,SMT/LOWER,FLIP</t>
   </si>
   <si>
-    <t>J2</t>
-  </si>
-  <si>
     <t>FPCC-0.5P-34.1*6.1-60-CW</t>
   </si>
   <si>
+    <t>IMSA-12001S-60B-GFN1</t>
+  </si>
+  <si>
     <t>1.1.1.01.07.060</t>
   </si>
   <si>
-    <t>IMSA-12001S-60B-GFN1</t>
+    <t>J3</t>
   </si>
   <si>
     <t>CON,HSC,4-PIN</t>
   </si>
   <si>
-    <t>J3</t>
-  </si>
-  <si>
     <t>CONN-HSC-4</t>
   </si>
   <si>
+    <t>TAK-A4LMD</t>
+  </si>
+  <si>
     <t>1.1.1.02.14.121</t>
   </si>
   <si>
-    <t>TAK-A4LMD</t>
+    <t>L1</t>
   </si>
   <si>
     <t>IND,PWR,22uH,3.3A,7.7*7.2</t>
   </si>
   <si>
-    <t>L1</t>
-  </si>
-  <si>
     <t>INDC7.7*7.2</t>
   </si>
   <si>
+    <t>22uH</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.042</t>
   </si>
   <si>
-    <t>22uH</t>
+    <t>L2</t>
   </si>
   <si>
     <t>IND,PWR,4.7uH,6A,7*6.6</t>
   </si>
   <si>
-    <t>L2</t>
-  </si>
-  <si>
     <t>INDC7.2*6.6</t>
   </si>
   <si>
+    <t>4.7uH</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.049</t>
   </si>
   <si>
-    <t>4.7uH</t>
+    <t>L3</t>
   </si>
   <si>
     <t>IND,PWR,15uH@100KHz,20%,2.83A,10.5*10.3</t>
   </si>
   <si>
-    <t>L3</t>
-  </si>
-  <si>
     <t>INDM-10.5*10.3</t>
   </si>
   <si>
+    <t>15uH</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.012</t>
   </si>
   <si>
-    <t>15uH</t>
+    <t>L4</t>
   </si>
   <si>
     <t>TDK PWR 700Ω@100MHz 20% 4A 7.0*6.0</t>
   </si>
   <si>
-    <t>L4</t>
-  </si>
-  <si>
     <t>PMF7060</t>
   </si>
   <si>
+    <t>ACM7060-701-2PL</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.052A</t>
   </si>
   <si>
-    <t>ACM7060-701-2PL</t>
+    <t>L5, L6, L12, L13, L14, L16, L17, L18, L19, L20, L21, L22</t>
   </si>
   <si>
     <t>IND,CHOCK,90R@100MHz,25%,330mA,2.0*1.2*1.0</t>
   </si>
   <si>
-    <t>L5, L6, L12, L13, L14, L16, L17, L18, L19, L20, L21, L22</t>
-  </si>
-  <si>
     <t>INDC-CHOKE-0805</t>
   </si>
   <si>
+    <t>90R</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.035</t>
   </si>
   <si>
-    <t>90R</t>
+    <t>L7, L8, L9, L10, L11</t>
   </si>
   <si>
     <t>IND,PWR,0.47uH,6A,2.5*2.0</t>
   </si>
   <si>
-    <t>L7, L8, L9, L10, L11</t>
-  </si>
-  <si>
     <t>INDC-2.5*2</t>
   </si>
   <si>
+    <t>0.47uH</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.091</t>
   </si>
   <si>
-    <t>0.47uH</t>
+    <t>L15</t>
   </si>
   <si>
     <t>TDK PWR 800Ω@100MHz 20% 2A 4.5*3.2</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
     <t>PMF4532</t>
   </si>
   <si>
+    <t>ACM4532-801-2PL</t>
+  </si>
+  <si>
     <t>1.1.1.01.09.077</t>
   </si>
   <si>
-    <t>ACM4532-801-2PL</t>
+    <t>P1</t>
   </si>
   <si>
     <t>Header, 3-Pin</t>
   </si>
   <si>
-    <t>P1</t>
-  </si>
-  <si>
     <t>HDR1X3</t>
   </si>
   <si>
+    <t>P2</t>
+  </si>
+  <si>
     <t>Header, 3-Pin, Dual row</t>
   </si>
   <si>
-    <t>P2</t>
-  </si>
-  <si>
     <t>HDR2X3</t>
   </si>
   <si>
+    <t>Q1</t>
+  </si>
+  <si>
     <t>MOSFET,P,11A,55V,175mR,1,TO-252AA(DPAK)</t>
   </si>
   <si>
-    <t>Q1</t>
-  </si>
-  <si>
     <t>TO-2.29P-10*6.6-3</t>
   </si>
   <si>
+    <t>YJD18GP10A</t>
+  </si>
+  <si>
     <t>1.1.1.01.03.118</t>
   </si>
   <si>
-    <t>YJD18GP10A</t>
+    <t>Q2, Q3, Q7, Q8</t>
   </si>
   <si>
     <t>MOSFET,N,115mA,60V,7.5R,SOT23</t>
   </si>
   <si>
-    <t>Q2, Q3, Q7, Q8</t>
-  </si>
-  <si>
     <t>SOT-0.95P-2.9*2.4-3-L</t>
   </si>
   <si>
+    <t>2N7002</t>
+  </si>
+  <si>
     <t>1.1.1.01.03.071</t>
   </si>
   <si>
-    <t>2N7002</t>
+    <t>Q4</t>
   </si>
   <si>
     <t>BIP,PNP,500mA,150V,1,SOT-23(TO-236)/HIGH-VOLTAGE</t>
   </si>
   <si>
-    <t>Q4</t>
+    <t>MMBT5401LT1G</t>
   </si>
   <si>
     <t>1.6.1.01.004.003</t>
   </si>
   <si>
-    <t>MMBT5401LT1G</t>
+    <t>R1</t>
   </si>
   <si>
     <t>RES,GEN,150R,5%,250mW,1206</t>
   </si>
   <si>
-    <t>R1</t>
-  </si>
-  <si>
     <t>RESC-1206</t>
   </si>
   <si>
     <t>1.1.1.01.01.034</t>
   </si>
   <si>
+    <t>R2, R4, R11</t>
+  </si>
+  <si>
     <t>RES,GEN,91K,1%,62.5mW,0603, RES,GEN,1K,5%,100mW,0402, [NoValue]</t>
   </si>
   <si>
-    <t>R2, R4, R11</t>
-  </si>
-  <si>
     <t>RESC-0603</t>
   </si>
   <si>
+    <t>150K_1%, 1K_5%, 270R</t>
+  </si>
+  <si>
     <t>1.1.1.01.01.366, 1.1.1.01.01.064GJ, 1.1.1.01.01.511</t>
   </si>
   <si>
-    <t>150K_1%, 1K_5%, 270R</t>
+    <t>R3</t>
   </si>
   <si>
     <t>RES,GEN,10K,5%,100mW,0603</t>
   </si>
   <si>
-    <t>R3</t>
+    <t>10K</t>
   </si>
   <si>
     <t>1.1.1.01.01.065</t>
   </si>
   <si>
-    <t>10K</t>
+    <t>R5, R21, R80, R100, R106</t>
   </si>
   <si>
     <t>RES,GEN,10K,1%,100mW,0603, RES,GEN,200K,1%,100mW,0603, RES,GEN,20K,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R5, R21, R80, R100, R106</t>
+    <t>10K_1%, 200K, 20K_1%</t>
   </si>
   <si>
     <t>1.1.1.01.01.221-GJ, 1.1.1.01.01.266, 1.1.1.01.01.529</t>
   </si>
   <si>
-    <t>10K_1%, 200K, 20K_1%</t>
+    <t>R6</t>
   </si>
   <si>
     <t>RES,GEN,1.5K,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R6</t>
+    <t>1.5K</t>
   </si>
   <si>
     <t>1.1.1.01.01.268</t>
   </si>
   <si>
-    <t>1.5K</t>
+    <t>R7, R15, R17, R77</t>
   </si>
   <si>
     <t>RES,GEN,1K,5%,100mW,0402</t>
   </si>
   <si>
-    <t>R7, R15, R17, R77</t>
+    <t>1K_5%, DNP</t>
   </si>
   <si>
     <t>1.1.1.01.01.064GJ, 1.1.1.01.01.321</t>
   </si>
   <si>
-    <t>1K_5%, DNP</t>
+    <t>R8</t>
   </si>
   <si>
     <t>RES,GEN,44.2kΩ,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R8</t>
+    <t>44.2kΩ</t>
   </si>
   <si>
     <t>1.1.1.01.01.506</t>
   </si>
   <si>
-    <t>44.2kΩ</t>
+    <t>R9, R10</t>
   </si>
   <si>
     <t>RES,GEN,100K,5%,100mW,0603</t>
   </si>
   <si>
-    <t>R9, R10</t>
+    <t>100K</t>
   </si>
   <si>
     <t>1.1.1.01.01.139-GJ</t>
   </si>
   <si>
-    <t>100K</t>
+    <t>R12</t>
   </si>
   <si>
     <t>RES,GEN,60.4K,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R12</t>
+    <t>12K_1%</t>
   </si>
   <si>
     <t>1.1.1.01.01.276</t>
   </si>
   <si>
-    <t>12K_1%</t>
+    <t>R13</t>
   </si>
   <si>
     <t>RES,GEN,10R,5%,62.5mW,0603</t>
   </si>
   <si>
-    <t>R13</t>
+    <t>10R</t>
   </si>
   <si>
     <t>1.1.1.01.01.307</t>
   </si>
   <si>
-    <t>10R</t>
+    <t>R14</t>
   </si>
   <si>
     <t>RES,GEN,2K,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R14</t>
+    <t>2K</t>
   </si>
   <si>
     <t>1.1.1.01.01.159-GJ-jingmi</t>
   </si>
   <si>
-    <t>2K</t>
+    <t>R16</t>
   </si>
   <si>
     <t>RES MF 47K  1/16W 1% AEC-Q200 0402</t>
   </si>
   <si>
-    <t>R16</t>
+    <t>1%</t>
   </si>
   <si>
     <t>1.1.1.01.01.314</t>
   </si>
   <si>
-    <t>1%</t>
+    <t>R18, R40, R51, R56, R57, R66, R83, R85, R90, R92, R96, R99</t>
   </si>
   <si>
     <t>RES,GEN,56K,1%,62.5mW,0603</t>
   </si>
   <si>
-    <t>R18, R40, R51, R56, R57, R66, R83, R85, R90, R92, R96, R99</t>
+    <t>56K</t>
   </si>
   <si>
     <t>1.1.1.01.01.294</t>
   </si>
   <si>
-    <t>56K</t>
+    <t>R19</t>
   </si>
   <si>
     <t>RES MF 100 OHM 1/2W 1% 1206</t>
   </si>
   <si>
-    <t>R19</t>
+    <t>100R</t>
   </si>
   <si>
     <t>1.1.1.01.01.033GJ</t>
   </si>
   <si>
-    <t>100R</t>
+    <t>R20, R22, R33, R41, R75, R76, R84, R89, R114, R128, R130, R131, R137, R138, R139, R294</t>
   </si>
   <si>
     <t>RES,GEN,0R,5%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R20, R22, R33, R41, R75, R76, R84, R89, R114, R128, R130, R131, R137, R138, R139, R294</t>
+    <t>0R, DNP</t>
   </si>
   <si>
     <t>1.1.1.01.01.309</t>
   </si>
   <si>
-    <t>0R, DNP</t>
+    <t>R23, R113, R124, R2112, R2119</t>
   </si>
   <si>
     <t>RES MF 10K 1/16W 5% 0402, RES,GEN,10K,5%,62.5mW,0402, 通用厚膜电阻,10K,+/-5%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R23, R113, R124, R2112, R2119</t>
+    <t>10K_5%, 10K, [NoParam]</t>
   </si>
   <si>
     <t>1.1.1.01.01.290, [NoParam]</t>
   </si>
   <si>
-    <t>10K_5%, 10K, [NoParam]</t>
+    <t>R24, R42, R47, R71, R86, R88, R122, R125, R132</t>
   </si>
   <si>
     <t>RES,GEN,1K,5%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R24, R42, R47, R71, R86, R88, R122, R125, R132</t>
+    <t>1K, 1.3K</t>
   </si>
   <si>
     <t>1.1.1.01.01.321, 1.1.1.01.01.532</t>
   </si>
   <si>
-    <t>1K, 1.3K</t>
+    <t>R25</t>
   </si>
   <si>
     <t>RES,GEN,1.5K,5%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R25</t>
-  </si>
-  <si>
     <t>1.1.1.01.01.319</t>
   </si>
   <si>
+    <t>R26, R27, R49, R53</t>
+  </si>
+  <si>
     <t>RES,GEN,0R,5%,100mW,0603</t>
   </si>
   <si>
-    <t>R26, R27, R49, R53</t>
+    <t>0R</t>
   </si>
   <si>
     <t>1.1.1.01.01.269</t>
   </si>
   <si>
-    <t>0R</t>
+    <t>R28, R43, R118</t>
   </si>
   <si>
     <t>RES,GEN,200K,1%,62.5mW,0402, RES,GEN,200kΩ,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R28, R43, R118</t>
+    <t>200K, 200KΩ</t>
   </si>
   <si>
     <t>1.1.1.01.01.498</t>
   </si>
   <si>
-    <t>200K, 200KΩ</t>
+    <t>R29, R30, R44, R103, R129</t>
   </si>
   <si>
     <t>RES,GEN,100K,5%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R29, R30, R44, R103, R129</t>
-  </si>
-  <si>
     <t>1.1.1.01.01.313</t>
   </si>
   <si>
+    <t>R31</t>
+  </si>
+  <si>
     <t>RES,GEN,3.92kΩ,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R31</t>
+    <t>3.92KΩ</t>
   </si>
   <si>
     <t>1.1.1.01.01.469</t>
   </si>
   <si>
-    <t>3.92KΩ</t>
+    <t>R32</t>
   </si>
   <si>
     <t>RES,GEN,73.2K,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R32</t>
+    <t>73.2K</t>
   </si>
   <si>
     <t>1.1.1.01.01.255</t>
   </si>
   <si>
-    <t>73.2K</t>
+    <t>R34, R35</t>
   </si>
   <si>
     <t>RES,GEN,200R,1%,250mW,1206</t>
   </si>
   <si>
-    <t>R34, R35</t>
+    <t>200R</t>
   </si>
   <si>
     <t>1.1.1.01.01.036-GJ</t>
   </si>
   <si>
-    <t>200R</t>
+    <t>R36, R37, R38, R39, R67, R68, R81, R82, R116, R117</t>
   </si>
   <si>
     <t>RES,GEN,2.2kΩ,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R36, R37, R38, R39, R67, R68, R81, R82, R116, R117</t>
+    <t>2.2KΩ</t>
   </si>
   <si>
     <t>1.1.1.01.01.432</t>
   </si>
   <si>
-    <t>2.2KΩ</t>
-  </si>
-  <si>
     <t>R45</t>
   </si>
   <si>
+    <t>R46, R72, R104, R107, R109, R110, R112, R123</t>
+  </si>
+  <si>
     <t>RES,GEN,10K,5%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R46, R72, R104, R107, R109, R110, R112, R123</t>
+    <t>10K, 12K</t>
   </si>
   <si>
     <t>1.1.1.01.01.290, 1.1.1.01.01.320</t>
   </si>
   <si>
-    <t>10K, 12K</t>
+    <t>R48</t>
   </si>
   <si>
     <t>RES,GEN,10K,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R48</t>
-  </si>
-  <si>
     <t>1.1.1.01.01.221-GJ</t>
   </si>
   <si>
+    <t>R50, R52</t>
+  </si>
+  <si>
     <t>RES,GEN,60.4R,1%,250mW,1206</t>
   </si>
   <si>
-    <t>R50, R52</t>
+    <t>60.4R</t>
   </si>
   <si>
     <t>1.1.1.01.01.089</t>
   </si>
   <si>
-    <t>60.4R</t>
+    <t>R54</t>
   </si>
   <si>
     <t>RES,GEN,1K,5%,100mW,0603</t>
   </si>
   <si>
-    <t>R54</t>
+    <t>1K</t>
   </si>
   <si>
     <t>1.1.1.01.01.064-GJ</t>
   </si>
   <si>
-    <t>1K</t>
+    <t>R55, R58, R65, R79, R91, R93, R95</t>
   </si>
   <si>
     <t>RES,GEN,2.2K,5%,250mW,1206</t>
   </si>
   <si>
-    <t>R55, R58, R65, R79, R91, R93, R95</t>
+    <t>2.2K</t>
   </si>
   <si>
     <t>1.1.1.01.01.151</t>
   </si>
   <si>
-    <t>2.2K</t>
+    <t>R59</t>
   </si>
   <si>
     <t>RES,GEN,107K,1%,,0402</t>
   </si>
   <si>
-    <t>R59</t>
+    <t>107K</t>
   </si>
   <si>
     <t>1.1.1.01.01.386</t>
   </si>
   <si>
-    <t>107K</t>
+    <t>R60, R61, R101, R134, R135, R136, R140, R141, R142, R283, R284, R288</t>
   </si>
   <si>
     <t>RES,GEN,10k,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R60, R61, R101, R134, R135, R136, R140, R141, R142, R283, R284, R288</t>
+    <t>NC, 10K, DNP</t>
   </si>
   <si>
     <t>1.1.1.01.01.392</t>
   </si>
   <si>
-    <t>NC, 10K, DNP</t>
+    <t>R62</t>
   </si>
   <si>
     <t>RES,GEN,100R,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R62</t>
-  </si>
-  <si>
     <t>1.1.1.01.01.315</t>
   </si>
   <si>
+    <t>R63</t>
+  </si>
+  <si>
     <t>RES,GEN,182K,1%,,0402</t>
   </si>
   <si>
-    <t>R63</t>
+    <t>182K</t>
   </si>
   <si>
     <t>1.1.1.01.01.504</t>
   </si>
   <si>
-    <t>182K</t>
+    <t>R64, R98</t>
   </si>
   <si>
     <t>RES,GEN,1M,5%,100mW,0603</t>
   </si>
   <si>
-    <t>R64, R98</t>
+    <t>1M</t>
   </si>
   <si>
     <t>1.1.1.01.01.166-GJ</t>
   </si>
   <si>
-    <t>1M</t>
+    <t>R69</t>
   </si>
   <si>
     <t>RES,GEN,31.6K,1%,,0402</t>
   </si>
   <si>
-    <t>R69</t>
+    <t>31.6K</t>
   </si>
   <si>
     <t>1.1.1.01.01.387</t>
   </si>
   <si>
-    <t>31.6K</t>
+    <t>R70, R155, R156, R313, R314</t>
   </si>
   <si>
     <t>RES,GEN,4.7K,5%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R70, R155, R156, R313, R314</t>
+    <t>4.7K</t>
   </si>
   <si>
     <t>1.1.1.01.01.311</t>
   </si>
   <si>
-    <t>4.7K</t>
+    <t>R73, R2105, R2114, R2115, R2117, R2118, R2120, R2121, R2122</t>
   </si>
   <si>
     <t>RES,GEN,0R,5%,62.5mW,0402, 通用厚膜电阻,0R,+/-5%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R73, R2105, R2114, R2115, R2117, R2118, R2120, R2121, R2122</t>
+    <t>0R, [NoParam]</t>
   </si>
   <si>
     <t>1.1.1.01.01.309, [NoParam]</t>
   </si>
   <si>
-    <t>0R, [NoParam]</t>
+    <t>R78</t>
   </si>
   <si>
     <t>RES,GEN,1MR,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R78</t>
+    <t>1MR</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>1MR</t>
+    <t>R87, R127</t>
   </si>
   <si>
     <t>RES,GEN,4.3kΩ,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R87, R127</t>
+    <t>4.3KΩ, 1.6KΩ</t>
   </si>
   <si>
     <t>1.1.1.01.01.419, 1.1.1.01.01.385</t>
   </si>
   <si>
-    <t>4.3KΩ, 1.6KΩ</t>
+    <t>R94</t>
   </si>
   <si>
     <t>RES,GEN,4.7K,5%,100mW,0603</t>
   </si>
   <si>
-    <t>R94</t>
-  </si>
-  <si>
     <t>1.1.1.01.01.104-GJ</t>
   </si>
   <si>
+    <t>R97, R102</t>
+  </si>
+  <si>
     <t>RES,GEN,330R,5%,1W,2512</t>
   </si>
   <si>
-    <t>R97, R102</t>
-  </si>
-  <si>
     <t>RESC-2512</t>
   </si>
   <si>
+    <t>330R</t>
+  </si>
+  <si>
     <t>1.1.1.01.01.211</t>
   </si>
   <si>
-    <t>330R</t>
+    <t>R105</t>
   </si>
   <si>
     <t>RES,GEN,100K,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R105</t>
-  </si>
-  <si>
     <t>1.1.1.01.01.259</t>
   </si>
   <si>
+    <t>R111</t>
+  </si>
+  <si>
     <t>RES,GEN,6.04K,1%,100mW,0603</t>
   </si>
   <si>
-    <t>R111</t>
+    <t>6.04K</t>
   </si>
   <si>
     <t>1.1.1.01.01.121GJ</t>
   </si>
   <si>
-    <t>6.04K</t>
+    <t>R115</t>
   </si>
   <si>
     <t>RES,GEN,1M,1%,62.5mW,0603</t>
   </si>
   <si>
-    <t>R115</t>
-  </si>
-  <si>
     <t>1.1.1.01.01.301</t>
   </si>
   <si>
+    <t>R119, R120</t>
+  </si>
+  <si>
     <t>RES,GEN,1R,5%,100mW,0603</t>
   </si>
   <si>
-    <t>R119, R120</t>
+    <t>1R</t>
   </si>
   <si>
     <t>1.1.1.01.01.063</t>
   </si>
   <si>
-    <t>1R</t>
+    <t>R126, R1905</t>
   </si>
   <si>
     <t>通用厚膜电阻,10K,+/-5%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R126, R1905</t>
-  </si>
-  <si>
     <t>R0402</t>
   </si>
   <si>
+    <t>R133</t>
+  </si>
+  <si>
     <t>RES,GEN,45.3kΩ,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R133</t>
+    <t>45.3KΩ</t>
   </si>
   <si>
     <t>1.1.1.01.01.472</t>
   </si>
   <si>
-    <t>45.3KΩ</t>
+    <t>R147, R148, R316, R318</t>
   </si>
   <si>
     <t>RES,GEN,22R,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R147, R148, R316, R318</t>
+    <t>22R</t>
   </si>
   <si>
     <t>1.1.1.01.01.312</t>
   </si>
   <si>
-    <t>22R</t>
+    <t>R1100</t>
   </si>
   <si>
     <t>通用厚膜电阻,33R,+/-5%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R1100</t>
+    <t>R1110</t>
   </si>
   <si>
     <t>通用厚膜电阻,0R,+/-5%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R1110</t>
+    <t>R1301, R1808, R1809, R1810, R1811, R1812, R1813</t>
   </si>
   <si>
     <t>通用厚膜电阻,22R,+/-5%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R1301, R1808, R1809, R1810, R1811, R1812, R1813</t>
+    <t>R1400</t>
   </si>
   <si>
     <t>通用厚膜电阻,133R,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R1400</t>
+    <t>R1401, R1702, R1703</t>
   </si>
   <si>
     <t>通用厚膜电阻,1R,+/-1%,R0603,1/10W.</t>
   </si>
   <si>
-    <t>R1401, R1702, R1703</t>
-  </si>
-  <si>
     <t>R0603</t>
   </si>
   <si>
+    <t>R1402, R1403</t>
+  </si>
+  <si>
     <t>厚膜低阻值电阻,0R1,+/-1%,R0603,1/10W.</t>
   </si>
   <si>
-    <t>R1402, R1403</t>
+    <t>R1608, R1701</t>
   </si>
   <si>
     <t>通用厚膜电阻,2K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R1608, R1701</t>
+    <t>R1900, R1901</t>
   </si>
   <si>
     <t>通用厚膜电阻,240R,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R1900, R1901</t>
+    <t>R1904, R1906</t>
   </si>
   <si>
     <t>通用厚膜电阻,1K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R1904, R1906</t>
+    <t>R1908, R1909</t>
   </si>
   <si>
     <t>通用厚膜电阻,49R9,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R1908, R1909</t>
+    <t>R2100, R2101</t>
   </si>
   <si>
     <t>通用厚膜电阻,100R,+/-5%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R2100, R2101</t>
+    <t>R2102</t>
   </si>
   <si>
     <t>RES,GEN,68K,1%,62.5mW,0402</t>
   </si>
   <si>
-    <t>R2102</t>
+    <t>68K</t>
   </si>
   <si>
     <t>1.1.1.01.01.371</t>
   </si>
   <si>
-    <t>68K</t>
+    <t>R2103</t>
   </si>
   <si>
     <t>通用厚膜电阻,120K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R2103</t>
+    <t>R2108, R2110</t>
   </si>
   <si>
     <t>通用厚膜电阻,2K2,+/-5%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R2108, R2110</t>
+    <t>R2113</t>
   </si>
   <si>
     <t>通用厚膜电阻,110K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R2113</t>
+    <t>R2116</t>
   </si>
   <si>
     <t>通用厚膜电阻,49.9K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
-    <t>R2116</t>
-  </si>
-  <si>
     <t>49.9k</t>
   </si>
   <si>
+    <t>RN1, RN4, RN5</t>
+  </si>
+  <si>
     <t>RES,NET,33R,5%,62.5mW,0402_4</t>
   </si>
   <si>
-    <t>RN1, RN4, RN5</t>
-  </si>
-  <si>
     <t>RESCA-0.5P-0402-8</t>
   </si>
   <si>
+    <t>33R</t>
+  </si>
+  <si>
     <t>1.1.1.01.01.324</t>
   </si>
   <si>
-    <t>33R</t>
+    <t>SC1, SC2, SC3, SC4</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>SC1, SC2, SC3, SC4</t>
-  </si>
-  <si>
     <t>SHIELD_CAN_CLIP$2F$PTV0703B</t>
   </si>
   <si>
@@ -1553,57 +1553,57 @@
     <t>Z-shrapnel</t>
   </si>
   <si>
+    <t>Z型金属弹片</t>
+  </si>
+  <si>
     <t>1.1.2.276.009</t>
   </si>
   <si>
-    <t>Z型金属弹片</t>
+    <t>SPK1</t>
   </si>
   <si>
     <t>SPEAKER,94dB,400Hz-10KHz,50R,34MM</t>
   </si>
   <si>
-    <t>SPK1</t>
-  </si>
-  <si>
     <t>SPK-3P-36*15.9</t>
   </si>
   <si>
+    <t>UGSP3750-06</t>
+  </si>
+  <si>
     <t>1.1.1.02.09.027</t>
   </si>
   <si>
-    <t>UGSP3750-06</t>
+    <t>TVS1, TVS2, TVS3, TVS4, TVS5, TVS6, TVS7, TVS8, TVS9, TVS10</t>
   </si>
   <si>
     <t>TVS,5.0V,80W,2,SOD-923, TVS,3.3V,300mW,2,SOD-923</t>
   </si>
   <si>
-    <t>TVS1, TVS2, TVS3, TVS4, TVS5, TVS6, TVS7, TVS8, TVS9, TVS10</t>
-  </si>
-  <si>
     <t>SOD-1*0.6</t>
   </si>
   <si>
+    <t>ESD9B5.0ST5G, SZESD9101P2T5G(ON Semi)</t>
+  </si>
+  <si>
     <t>1.1.1.01.03.073</t>
   </si>
   <si>
-    <t>ESD9B5.0ST5G, SZESD9101P2T5G(ON Semi)</t>
+    <t>U1</t>
   </si>
   <si>
     <t>MPQ3367GR–AEC1-Z</t>
   </si>
   <si>
-    <t>U1</t>
-  </si>
-  <si>
     <t>QFN-0.5P-4*4_HS-24N</t>
   </si>
   <si>
+    <t>U2</t>
+  </si>
+  <si>
     <t>IC ,MPQ4323GDE-AEC1-Z</t>
   </si>
   <si>
-    <t>U2</t>
-  </si>
-  <si>
     <t>QFN12_MPQ4323_MNP</t>
   </si>
   <si>
@@ -1613,120 +1613,120 @@
     <t>QFN-0.4P-7.5*7.5-64_HS</t>
   </si>
   <si>
+    <t>U4</t>
+  </si>
+  <si>
     <t>B1M family  32-bit ARM Cortex-M33 MCU with 1M pflash, 256K dflash and 128K SRAM, LQFP-64 package</t>
   </si>
   <si>
-    <t>U4</t>
-  </si>
-  <si>
     <t>LQFP64_10X10</t>
   </si>
   <si>
+    <t>U5, U15</t>
+  </si>
+  <si>
     <t>IC,Translator,2-bit bidirectional low voltage,TSSOP8</t>
   </si>
   <si>
-    <t>U5, U15</t>
-  </si>
-  <si>
     <t>SOP-0.65P-3*4.9-8</t>
   </si>
   <si>
+    <t>GTL2002DP</t>
+  </si>
+  <si>
     <t>1.1.1.01.05.170</t>
   </si>
   <si>
-    <t>GTL2002DP</t>
+    <t>U6</t>
   </si>
   <si>
     <t>IC FPD-Link III,CSI-2,WQFN64</t>
   </si>
   <si>
-    <t>U6</t>
-  </si>
-  <si>
     <t>QFN-0.5P-9*9-64-EPAD</t>
   </si>
   <si>
+    <t>DS90UB940-Q1</t>
+  </si>
+  <si>
     <t>1.1.1.01.05.299</t>
   </si>
   <si>
-    <t>DS90UB940-Q1</t>
+    <t>U7</t>
   </si>
   <si>
     <t>IC,CAN Tranceiver,High-speed/Standby mode,SO8</t>
   </si>
   <si>
-    <t>U7</t>
-  </si>
-  <si>
     <t>SOIC-1.27P-6*5-8</t>
   </si>
   <si>
+    <t>TCAN1042DRQ1</t>
+  </si>
+  <si>
     <t>1.1.1.01.05.255</t>
   </si>
   <si>
-    <t>TCAN1042DRQ1</t>
+    <t>U8</t>
   </si>
   <si>
     <t>IC,RTC,±5*10E-6,QFN10/with Temperature Compensation</t>
   </si>
   <si>
-    <t>U8</t>
-  </si>
-  <si>
     <t>QFN-0.7P-3.2*2.5-10</t>
   </si>
   <si>
+    <t>INS5609</t>
+  </si>
+  <si>
     <t>1.1.1.01.05.208A</t>
   </si>
   <si>
-    <t>INS5609</t>
+    <t>U9, U1902</t>
   </si>
   <si>
     <t>MPQ20051DQ-AEC1</t>
   </si>
   <si>
-    <t>U9, U1902</t>
-  </si>
-  <si>
     <t>QFN-0.65P-3.0*3.0-8</t>
   </si>
   <si>
+    <t>U11, U12, U13, U14, U19, U20</t>
+  </si>
+  <si>
     <t>IC,LEVEL SHIFTER/BUFFER,SOT-353</t>
   </si>
   <si>
-    <t>U11, U12, U13, U14, U19, U20</t>
-  </si>
-  <si>
     <t>SOT-0.65P-2*2.1-5</t>
   </si>
   <si>
+    <t>NLVVHC1GT126DF1G</t>
+  </si>
+  <si>
     <t>1.1.1.01.05.261</t>
   </si>
   <si>
-    <t>NLVVHC1GT126DF1G</t>
-  </si>
-  <si>
     <t>U16</t>
   </si>
   <si>
+    <t>U22</t>
+  </si>
+  <si>
     <t>IC,EEPROM,(2-wire) Serial EEPROM(I2C-bus),4Kbit,SOIC8</t>
   </si>
   <si>
-    <t>U22</t>
+    <t>BR24G16FJ-3GTE2</t>
   </si>
   <si>
     <t>1.1.1.01.05.307</t>
   </si>
   <si>
-    <t>BR24G16FJ-3GTE2</t>
+    <t>U1000</t>
   </si>
   <si>
     <t>ROCKCHIP SOC</t>
   </si>
   <si>
-    <t>U1000</t>
-  </si>
-  <si>
     <t>BGA418_14R00X14R00X1R24</t>
   </si>
   <si>
@@ -1742,106 +1742,106 @@
     <t>QFN68_7R00X7R00X0R80_T</t>
   </si>
   <si>
+    <t>U4100</t>
+  </si>
+  <si>
     <t>IC MEM NAND FLASH 8GB 2.7-3.6V EMMC 1.7-1.95V AEC-Q100 FBGA153</t>
   </si>
   <si>
-    <t>U4100</t>
-  </si>
-  <si>
     <t>FBGA153_0P5_11P5X13</t>
   </si>
   <si>
+    <t>KLM8G1GEUF-B04Q057</t>
+  </si>
+  <si>
     <t>1.1.1.01.05.404</t>
   </si>
   <si>
-    <t>KLM8G1GEUF-B04Q057</t>
+    <t>X1</t>
   </si>
   <si>
     <t>CON,32P,2R,TE BLUE,TE BLUE-32</t>
   </si>
   <si>
-    <t>X1</t>
-  </si>
-  <si>
     <t>CONN-TE BLUE-2137614-2-32</t>
   </si>
   <si>
+    <t>966658-2 /2137614-2</t>
+  </si>
+  <si>
     <t>1.1.1.02.14.059</t>
   </si>
   <si>
-    <t>966658-2 /2137614-2</t>
+    <t>XTD</t>
   </si>
   <si>
     <t>XTD Logo</t>
   </si>
   <si>
-    <t>XTD</t>
-  </si>
-  <si>
     <t>XTD-LOGO</t>
   </si>
   <si>
+    <t>Y1</t>
+  </si>
+  <si>
     <t>XTAL,24MHz, ±10PPM,3.2*2.5</t>
   </si>
   <si>
-    <t>Y1</t>
-  </si>
-  <si>
     <t>XTALC-3.2*2.5-4</t>
   </si>
   <si>
+    <t>24MHz</t>
+  </si>
+  <si>
     <t>1.1.1.01.08.017</t>
   </si>
   <si>
-    <t>24MHz</t>
+    <t>Y2</t>
   </si>
   <si>
     <t>XTAL,25MHz, ±10PPM,3.2*2.5</t>
   </si>
   <si>
-    <t>Y2</t>
+    <t>25MHz</t>
   </si>
   <si>
     <t>1.1.1.01.08.029</t>
   </si>
   <si>
-    <t>25MHz</t>
+    <t>Y1100</t>
   </si>
   <si>
     <t>无源晶振，24M，3225,±10ppm，8pF，Hosonic</t>
   </si>
   <si>
-    <t>Y1100</t>
-  </si>
-  <si>
     <t>CRY4_3R20X2R50X0R80</t>
   </si>
   <si>
+    <t>Y2100</t>
+  </si>
+  <si>
     <t>XTAL,32.768KHz,±10PPM,3.2*1.5*0.8</t>
   </si>
   <si>
-    <t>Y2100</t>
-  </si>
-  <si>
     <t>XTALC-3.2*1.5-2</t>
   </si>
   <si>
+    <t>32.768KHz</t>
+  </si>
+  <si>
     <t>1.1.1.01.08.022</t>
   </si>
   <si>
-    <t>32.768KHz</t>
+    <t>Z1, Z2</t>
   </si>
   <si>
     <t>TVS,27V,225mW,2,SOT-23</t>
   </si>
   <si>
-    <t>Z1, Z2</t>
+    <t>MMBZ27VCLT1G</t>
   </si>
   <si>
     <t>1.1.1.01.03.015</t>
-  </si>
-  <si>
-    <t>MMBZ27VCLT1G</t>
   </si>
 </sst>
 </file>
@@ -2217,7 +2217,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -2232,7 +2232,7 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -2262,7 +2262,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -2277,7 +2277,7 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -2307,7 +2307,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -2322,7 +2322,7 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -2352,7 +2352,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -2367,7 +2367,7 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -3233,7 +3233,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="17.375" customWidth="1"/>
-    <col min="4" max="5" width="14.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="14.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="32.75" customWidth="1"/>
     <col min="6" max="6" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3244,13 +3245,13 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -3264,13 +3265,13 @@
       <c r="B2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="7">
@@ -3284,13 +3285,13 @@
       <c r="B3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="10">
@@ -3304,13 +3305,13 @@
       <c r="B4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="10">
@@ -3324,14 +3325,14 @@
       <c r="B5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="F5" s="10">
         <v>45</v>
@@ -3344,13 +3345,13 @@
       <c r="B6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="10">
@@ -3364,13 +3365,13 @@
       <c r="B7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="10">
@@ -3378,17 +3379,17 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="8"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>34</v>
       </c>
+      <c r="E8" s="8"/>
       <c r="F8" s="10">
         <v>1</v>
       </c>
@@ -3400,13 +3401,13 @@
       <c r="B9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="10">
@@ -3420,13 +3421,13 @@
       <c r="B10" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="10">
@@ -3435,18 +3436,18 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="16" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="10">
@@ -3460,13 +3461,13 @@
       <c r="B12" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>47</v>
       </c>
       <c r="F12" s="10">
@@ -3475,19 +3476,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="16" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>34</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="F13" s="10">
         <v>3</v>
@@ -3500,13 +3501,13 @@
       <c r="B14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>52</v>
       </c>
       <c r="F14" s="10">
@@ -3520,14 +3521,14 @@
       <c r="B15" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="F15" s="10">
         <v>4</v>
@@ -3540,13 +3541,13 @@
       <c r="B16" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>60</v>
       </c>
       <c r="F16" s="10">
@@ -3560,13 +3561,13 @@
       <c r="B17" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>64</v>
       </c>
       <c r="F17" s="10">
@@ -3580,14 +3581,14 @@
       <c r="B18" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>47</v>
       </c>
       <c r="F18" s="10">
         <v>1</v>
@@ -3600,14 +3601,14 @@
       <c r="B19" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>64</v>
       </c>
       <c r="F19" s="10">
         <v>1</v>
@@ -3620,14 +3621,14 @@
       <c r="B20" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>73</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>47</v>
       </c>
       <c r="F20" s="10">
         <v>3</v>
@@ -3640,14 +3641,14 @@
       <c r="B21" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>76</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="F21" s="10">
         <v>2</v>
@@ -3660,13 +3661,13 @@
       <c r="B22" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>80</v>
       </c>
       <c r="F22" s="10">
@@ -3675,18 +3676,18 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="16" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="16" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="10">
@@ -3700,14 +3701,14 @@
       <c r="B24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="16" t="s">
         <v>84</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="F24" s="10">
         <v>3</v>
@@ -3720,13 +3721,13 @@
       <c r="B25" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="16" t="s">
         <v>89</v>
       </c>
       <c r="F25" s="10">
@@ -3740,14 +3741,14 @@
       <c r="B26" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="16" t="s">
         <v>92</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>64</v>
       </c>
       <c r="F26" s="10">
         <v>6</v>
@@ -3760,13 +3761,13 @@
       <c r="B27" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="16" t="s">
         <v>96</v>
       </c>
       <c r="F27" s="10">
@@ -3780,14 +3781,14 @@
       <c r="B28" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>99</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>52</v>
       </c>
       <c r="F28" s="10">
         <v>5</v>
@@ -3800,14 +3801,14 @@
       <c r="B29" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="16" t="s">
         <v>102</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>14</v>
       </c>
       <c r="F29" s="10">
         <v>1</v>
@@ -3820,11 +3821,11 @@
       <c r="B30" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
       <c r="F30" s="10">
         <v>10</v>
       </c>
@@ -3836,11 +3837,11 @@
       <c r="B31" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="10">
         <v>75</v>
       </c>
@@ -3852,14 +3853,14 @@
       <c r="B32" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>14</v>
       </c>
       <c r="F32" s="10">
         <v>3</v>
@@ -3872,13 +3873,13 @@
       <c r="B33" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>114</v>
       </c>
       <c r="F33" s="10">
@@ -3892,11 +3893,11 @@
       <c r="B34" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
       <c r="F34" s="10">
         <v>2</v>
       </c>
@@ -3908,11 +3909,11 @@
       <c r="B35" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
       <c r="F35" s="10">
         <v>2</v>
       </c>
@@ -3924,11 +3925,11 @@
       <c r="B36" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="10">
         <v>8</v>
       </c>
@@ -3940,14 +3941,14 @@
       <c r="B37" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>123</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>32</v>
       </c>
       <c r="F37" s="10">
         <v>2</v>
@@ -3960,13 +3961,13 @@
       <c r="B38" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="16" t="s">
         <v>127</v>
       </c>
       <c r="F38" s="10">
@@ -3980,13 +3981,13 @@
       <c r="B39" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="16" t="s">
         <v>131</v>
       </c>
       <c r="F39" s="10">
@@ -4000,14 +4001,14 @@
       <c r="B40" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="16" t="s">
         <v>134</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="F40" s="10">
         <v>1</v>
@@ -4020,11 +4021,11 @@
       <c r="B41" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="10">
         <v>2</v>
       </c>
@@ -4036,11 +4037,11 @@
       <c r="B42" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
       <c r="F42" s="10">
         <v>2</v>
       </c>
@@ -4052,11 +4053,11 @@
       <c r="B43" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
       <c r="F43" s="10">
         <v>1</v>
       </c>
@@ -4068,14 +4069,14 @@
       <c r="B44" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="16" t="s">
         <v>145</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="F44" s="10">
         <v>2</v>
@@ -4088,11 +4089,11 @@
       <c r="B45" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
       <c r="F45" s="10">
         <v>1</v>
       </c>
@@ -4104,27 +4105,27 @@
       <c r="B46" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="16" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
       <c r="F47" s="10">
         <v>3</v>
       </c>
@@ -4136,27 +4137,27 @@
       <c r="B48" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
       <c r="F48" s="10">
         <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="16" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="C49" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
       <c r="F49" s="10">
         <v>2</v>
       </c>
@@ -4168,11 +4169,11 @@
       <c r="B50" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
       <c r="F50" s="10">
         <v>5</v>
       </c>
@@ -4184,27 +4185,27 @@
       <c r="B51" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="16" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="C52" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
       <c r="F52" s="10">
         <v>2</v>
       </c>
@@ -4216,13 +4217,13 @@
       <c r="B53" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="16" t="s">
         <v>163</v>
       </c>
       <c r="F53" s="10">
@@ -4236,13 +4237,13 @@
       <c r="B54" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="16" t="s">
         <v>168</v>
       </c>
       <c r="F54" s="10">
@@ -4256,13 +4257,13 @@
       <c r="B55" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="16" t="s">
         <v>173</v>
       </c>
       <c r="F55" s="10">
@@ -4276,13 +4277,13 @@
       <c r="B56" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="16" t="s">
         <v>177</v>
       </c>
       <c r="F56" s="10">
@@ -4296,13 +4297,13 @@
       <c r="B57" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="16" t="s">
         <v>182</v>
       </c>
       <c r="F57" s="10">
@@ -4316,11 +4317,11 @@
       <c r="B58" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
       <c r="F58" s="10">
         <v>2</v>
       </c>
@@ -4332,13 +4333,13 @@
       <c r="B59" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="16" t="s">
         <v>190</v>
       </c>
       <c r="F59" s="10">
@@ -4352,13 +4353,13 @@
       <c r="B60" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="16" t="s">
         <v>195</v>
       </c>
       <c r="F60" s="10">
@@ -4372,11 +4373,11 @@
       <c r="B61" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
       <c r="F61" s="10">
         <v>4</v>
       </c>
@@ -4388,13 +4389,13 @@
       <c r="B62" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="16" t="s">
         <v>203</v>
       </c>
       <c r="F62" s="10">
@@ -4408,13 +4409,13 @@
       <c r="B63" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="16" t="s">
         <v>208</v>
       </c>
       <c r="F63" s="10">
@@ -4428,13 +4429,13 @@
       <c r="B64" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="16" t="s">
         <v>213</v>
       </c>
       <c r="F64" s="10">
@@ -4448,13 +4449,13 @@
       <c r="B65" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="16" t="s">
         <v>218</v>
       </c>
       <c r="F65" s="10">
@@ -4468,13 +4469,13 @@
       <c r="B66" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="16" t="s">
         <v>223</v>
       </c>
       <c r="F66" s="10">
@@ -4488,13 +4489,13 @@
       <c r="B67" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="16" t="s">
         <v>228</v>
       </c>
       <c r="F67" s="10">
@@ -4508,13 +4509,13 @@
       <c r="B68" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E68" s="16" t="s">
         <v>233</v>
       </c>
       <c r="F68" s="10">
@@ -4528,13 +4529,13 @@
       <c r="B69" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="16" t="s">
         <v>238</v>
       </c>
       <c r="F69" s="10">
@@ -4548,13 +4549,13 @@
       <c r="B70" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="C70" s="17" t="s">
+      <c r="C70" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="16" t="s">
         <v>243</v>
       </c>
       <c r="F70" s="10">
@@ -4568,13 +4569,13 @@
       <c r="B71" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E71" s="16" t="s">
         <v>248</v>
       </c>
       <c r="F71" s="10">
@@ -4588,11 +4589,11 @@
       <c r="B72" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
       <c r="F72" s="10">
         <v>1</v>
       </c>
@@ -4604,11 +4605,11 @@
       <c r="B73" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
       <c r="F73" s="10">
         <v>1</v>
       </c>
@@ -4620,13 +4621,13 @@
       <c r="B74" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="C74" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="D74" s="17" t="s">
+      <c r="D74" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="E74" s="17" t="s">
+      <c r="E74" s="16" t="s">
         <v>259</v>
       </c>
       <c r="F74" s="10">
@@ -4640,13 +4641,13 @@
       <c r="B75" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="C75" s="17" t="s">
+      <c r="C75" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" s="16" t="s">
         <v>264</v>
       </c>
       <c r="F75" s="10">
@@ -4660,13 +4661,13 @@
       <c r="B76" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="C76" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="E76" s="17" t="s">
+      <c r="E76" s="16" t="s">
         <v>268</v>
       </c>
       <c r="F76" s="10">
@@ -4680,14 +4681,14 @@
       <c r="B77" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="C77" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E77" s="16" t="s">
         <v>272</v>
-      </c>
-      <c r="E77" s="17" t="s">
-        <v>34</v>
       </c>
       <c r="F77" s="10">
         <v>1</v>
@@ -4700,13 +4701,13 @@
       <c r="B78" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="C78" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="D78" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E78" s="16" t="s">
         <v>277</v>
       </c>
       <c r="F78" s="10">
@@ -4720,13 +4721,13 @@
       <c r="B79" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C79" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="16" t="s">
         <v>281</v>
       </c>
       <c r="F79" s="10">
@@ -4740,13 +4741,13 @@
       <c r="B80" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C80" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D80" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="E80" s="17" t="s">
+      <c r="E80" s="16" t="s">
         <v>285</v>
       </c>
       <c r="F80" s="10">
@@ -4760,13 +4761,13 @@
       <c r="B81" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="C81" s="17" t="s">
+      <c r="C81" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E81" s="16" t="s">
         <v>289</v>
       </c>
       <c r="F81" s="10">
@@ -4780,13 +4781,13 @@
       <c r="B82" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="E82" s="17" t="s">
+      <c r="E82" s="16" t="s">
         <v>293</v>
       </c>
       <c r="F82" s="10">
@@ -4800,13 +4801,13 @@
       <c r="B83" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="E83" s="17" t="s">
+      <c r="E83" s="16" t="s">
         <v>297</v>
       </c>
       <c r="F83" s="10">
@@ -4820,13 +4821,13 @@
       <c r="B84" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="C84" s="17" t="s">
+      <c r="C84" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="E84" s="17" t="s">
+      <c r="E84" s="16" t="s">
         <v>301</v>
       </c>
       <c r="F84" s="10">
@@ -4840,13 +4841,13 @@
       <c r="B85" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C85" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="E85" s="17" t="s">
+      <c r="E85" s="16" t="s">
         <v>305</v>
       </c>
       <c r="F85" s="10">
@@ -4860,13 +4861,13 @@
       <c r="B86" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="E86" s="17" t="s">
+      <c r="E86" s="16" t="s">
         <v>309</v>
       </c>
       <c r="F86" s="10">
@@ -4880,13 +4881,13 @@
       <c r="B87" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="C87" s="17" t="s">
+      <c r="C87" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="E87" s="17" t="s">
+      <c r="E87" s="16" t="s">
         <v>313</v>
       </c>
       <c r="F87" s="10">
@@ -4900,13 +4901,13 @@
       <c r="B88" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="C88" s="17" t="s">
+      <c r="C88" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D88" s="17" t="s">
+      <c r="D88" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="E88" s="17" t="s">
+      <c r="E88" s="16" t="s">
         <v>317</v>
       </c>
       <c r="F88" s="10">
@@ -4920,13 +4921,13 @@
       <c r="B89" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="C89" s="17" t="s">
+      <c r="C89" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D89" s="17" t="s">
+      <c r="D89" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="E89" s="16" t="s">
         <v>321</v>
       </c>
       <c r="F89" s="10">
@@ -4940,13 +4941,13 @@
       <c r="B90" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="C90" s="17" t="s">
+      <c r="C90" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="D90" s="17" t="s">
+      <c r="D90" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="E90" s="17" t="s">
+      <c r="E90" s="16" t="s">
         <v>325</v>
       </c>
       <c r="F90" s="10">
@@ -4960,13 +4961,13 @@
       <c r="B91" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="C91" s="17" t="s">
+      <c r="C91" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D91" s="17" t="s">
+      <c r="D91" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="E91" s="16" t="s">
         <v>329</v>
       </c>
       <c r="F91" s="10">
@@ -4980,13 +4981,13 @@
       <c r="B92" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="C92" s="17" t="s">
+      <c r="C92" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D92" s="17" t="s">
+      <c r="D92" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="E92" s="17" t="s">
+      <c r="E92" s="16" t="s">
         <v>333</v>
       </c>
       <c r="F92" s="10">
@@ -5000,13 +5001,13 @@
       <c r="B93" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="C93" s="17" t="s">
+      <c r="C93" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D93" s="17" t="s">
+      <c r="D93" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="E93" s="17" t="s">
+      <c r="E93" s="16" t="s">
         <v>337</v>
       </c>
       <c r="F93" s="10">
@@ -5020,14 +5021,14 @@
       <c r="B94" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="C94" s="17" t="s">
+      <c r="C94" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D94" s="17" t="s">
+      <c r="D94" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="E94" s="16" t="s">
         <v>340</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>289</v>
       </c>
       <c r="F94" s="10">
         <v>1</v>
@@ -5040,13 +5041,13 @@
       <c r="B95" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D95" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="E95" s="17" t="s">
+      <c r="E95" s="16" t="s">
         <v>344</v>
       </c>
       <c r="F95" s="10">
@@ -5060,13 +5061,13 @@
       <c r="B96" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="C96" s="17" t="s">
+      <c r="C96" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D96" s="17" t="s">
+      <c r="D96" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="E96" s="17" t="s">
+      <c r="E96" s="16" t="s">
         <v>348</v>
       </c>
       <c r="F96" s="10">
@@ -5080,14 +5081,14 @@
       <c r="B97" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="C97" s="17" t="s">
+      <c r="C97" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D97" s="17" t="s">
+      <c r="D97" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="E97" s="16" t="s">
         <v>351</v>
-      </c>
-      <c r="E97" s="17" t="s">
-        <v>301</v>
       </c>
       <c r="F97" s="10">
         <v>5</v>
@@ -5100,13 +5101,13 @@
       <c r="B98" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="C98" s="17" t="s">
+      <c r="C98" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D98" s="17" t="s">
+      <c r="D98" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="E98" s="17" t="s">
+      <c r="E98" s="16" t="s">
         <v>355</v>
       </c>
       <c r="F98" s="10">
@@ -5120,13 +5121,13 @@
       <c r="B99" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="C99" s="17" t="s">
+      <c r="C99" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D99" s="17" t="s">
+      <c r="D99" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="E99" s="17" t="s">
+      <c r="E99" s="16" t="s">
         <v>359</v>
       </c>
       <c r="F99" s="10">
@@ -5140,13 +5141,13 @@
       <c r="B100" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="C100" s="17" t="s">
+      <c r="C100" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="E100" s="17" t="s">
+      <c r="E100" s="16" t="s">
         <v>363</v>
       </c>
       <c r="F100" s="10">
@@ -5160,13 +5161,13 @@
       <c r="B101" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="C101" s="17" t="s">
+      <c r="C101" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D101" s="17" t="s">
+      <c r="D101" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="E101" s="17" t="s">
+      <c r="E101" s="16" t="s">
         <v>367</v>
       </c>
       <c r="F101" s="10">
@@ -5175,18 +5176,18 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="16" t="s">
-        <v>310</v>
+        <v>368</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="C102" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="C102" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D102" s="17" t="s">
+      <c r="D102" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="E102" s="17" t="s">
+      <c r="E102" s="16" t="s">
         <v>313</v>
       </c>
       <c r="F102" s="10">
@@ -5200,13 +5201,13 @@
       <c r="B103" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="C103" s="17" t="s">
+      <c r="C103" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D103" s="17" t="s">
+      <c r="D103" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="E103" s="17" t="s">
+      <c r="E103" s="16" t="s">
         <v>372</v>
       </c>
       <c r="F103" s="10">
@@ -5220,14 +5221,14 @@
       <c r="B104" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="C104" s="17" t="s">
+      <c r="C104" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D104" s="17" t="s">
+      <c r="D104" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="E104" s="16" t="s">
         <v>375</v>
-      </c>
-      <c r="E104" s="17" t="s">
-        <v>281</v>
       </c>
       <c r="F104" s="10">
         <v>1</v>
@@ -5240,13 +5241,13 @@
       <c r="B105" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C105" s="17" t="s">
+      <c r="C105" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="D105" s="17" t="s">
+      <c r="D105" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="E105" s="17" t="s">
+      <c r="E105" s="16" t="s">
         <v>379</v>
       </c>
       <c r="F105" s="10">
@@ -5260,13 +5261,13 @@
       <c r="B106" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="C106" s="17" t="s">
+      <c r="C106" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D106" s="17" t="s">
+      <c r="D106" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="E106" s="17" t="s">
+      <c r="E106" s="16" t="s">
         <v>383</v>
       </c>
       <c r="F106" s="10">
@@ -5280,13 +5281,13 @@
       <c r="B107" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="C107" s="17" t="s">
+      <c r="C107" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="D107" s="17" t="s">
+      <c r="D107" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="E107" s="17" t="s">
+      <c r="E107" s="16" t="s">
         <v>387</v>
       </c>
       <c r="F107" s="10">
@@ -5300,13 +5301,13 @@
       <c r="B108" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="C108" s="17" t="s">
+      <c r="C108" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D108" s="17" t="s">
+      <c r="D108" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="E108" s="17" t="s">
+      <c r="E108" s="16" t="s">
         <v>391</v>
       </c>
       <c r="F108" s="10">
@@ -5320,13 +5321,13 @@
       <c r="B109" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="C109" s="17" t="s">
+      <c r="C109" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D109" s="17" t="s">
+      <c r="D109" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="E109" s="17" t="s">
+      <c r="E109" s="16" t="s">
         <v>395</v>
       </c>
       <c r="F109" s="10">
@@ -5340,14 +5341,14 @@
       <c r="B110" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="C110" s="17" t="s">
+      <c r="C110" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D110" s="17" t="s">
+      <c r="D110" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="E110" s="16" t="s">
         <v>398</v>
-      </c>
-      <c r="E110" s="17" t="s">
-        <v>325</v>
       </c>
       <c r="F110" s="10">
         <v>1</v>
@@ -5360,13 +5361,13 @@
       <c r="B111" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="C111" s="17" t="s">
+      <c r="C111" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D111" s="17" t="s">
+      <c r="D111" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E111" s="17" t="s">
+      <c r="E111" s="16" t="s">
         <v>402</v>
       </c>
       <c r="F111" s="10">
@@ -5380,13 +5381,13 @@
       <c r="B112" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="C112" s="17" t="s">
+      <c r="C112" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D112" s="17" t="s">
+      <c r="D112" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="E112" s="17" t="s">
+      <c r="E112" s="16" t="s">
         <v>406</v>
       </c>
       <c r="F112" s="10">
@@ -5400,13 +5401,13 @@
       <c r="B113" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="C113" s="17" t="s">
+      <c r="C113" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D113" s="17" t="s">
+      <c r="D113" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="E113" s="17" t="s">
+      <c r="E113" s="16" t="s">
         <v>410</v>
       </c>
       <c r="F113" s="10">
@@ -5420,13 +5421,13 @@
       <c r="B114" s="17" t="s">
         <v>412</v>
       </c>
-      <c r="C114" s="17" t="s">
+      <c r="C114" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D114" s="17" t="s">
+      <c r="D114" s="16" t="s">
         <v>413</v>
       </c>
-      <c r="E114" s="17" t="s">
+      <c r="E114" s="16" t="s">
         <v>414</v>
       </c>
       <c r="F114" s="10">
@@ -5440,13 +5441,13 @@
       <c r="B115" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="C115" s="17" t="s">
+      <c r="C115" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D115" s="17" t="s">
+      <c r="D115" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="E115" s="17" t="s">
+      <c r="E115" s="16" t="s">
         <v>418</v>
       </c>
       <c r="F115" s="10">
@@ -5460,13 +5461,13 @@
       <c r="B116" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="C116" s="17" t="s">
+      <c r="C116" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D116" s="17" t="s">
+      <c r="D116" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="E116" s="17" t="s">
+      <c r="E116" s="16" t="s">
         <v>422</v>
       </c>
       <c r="F116" s="10">
@@ -5480,13 +5481,13 @@
       <c r="B117" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="C117" s="17" t="s">
+      <c r="C117" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D117" s="17" t="s">
+      <c r="D117" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="E117" s="17" t="s">
+      <c r="E117" s="16" t="s">
         <v>426</v>
       </c>
       <c r="F117" s="10">
@@ -5500,14 +5501,14 @@
       <c r="B118" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="C118" s="17" t="s">
+      <c r="C118" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D118" s="17" t="s">
+      <c r="D118" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="E118" s="16" t="s">
         <v>429</v>
-      </c>
-      <c r="E118" s="17" t="s">
-        <v>414</v>
       </c>
       <c r="F118" s="10">
         <v>1</v>
@@ -5520,13 +5521,13 @@
       <c r="B119" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="C119" s="17" t="s">
+      <c r="C119" s="16" t="s">
         <v>432</v>
       </c>
-      <c r="D119" s="17" t="s">
+      <c r="D119" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="E119" s="17" t="s">
+      <c r="E119" s="16" t="s">
         <v>434</v>
       </c>
       <c r="F119" s="10">
@@ -5540,14 +5541,14 @@
       <c r="B120" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="C120" s="17" t="s">
+      <c r="C120" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D120" s="17" t="s">
+      <c r="D120" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="E120" s="16" t="s">
         <v>437</v>
-      </c>
-      <c r="E120" s="17" t="s">
-        <v>301</v>
       </c>
       <c r="F120" s="10">
         <v>1</v>
@@ -5560,13 +5561,13 @@
       <c r="B121" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="C121" s="17" t="s">
+      <c r="C121" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D121" s="17" t="s">
+      <c r="D121" s="16" t="s">
         <v>440</v>
       </c>
-      <c r="E121" s="17" t="s">
+      <c r="E121" s="16" t="s">
         <v>441</v>
       </c>
       <c r="F121" s="10">
@@ -5580,14 +5581,14 @@
       <c r="B122" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="C122" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D122" s="17" t="s">
+      <c r="D122" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="E122" s="16" t="s">
         <v>444</v>
-      </c>
-      <c r="E122" s="17" t="s">
-        <v>406</v>
       </c>
       <c r="F122" s="10">
         <v>1</v>
@@ -5600,13 +5601,13 @@
       <c r="B123" s="17" t="s">
         <v>446</v>
       </c>
-      <c r="C123" s="17" t="s">
+      <c r="C123" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="D123" s="17" t="s">
+      <c r="D123" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="E123" s="17" t="s">
+      <c r="E123" s="16" t="s">
         <v>448</v>
       </c>
       <c r="F123" s="10">
@@ -5620,11 +5621,11 @@
       <c r="B124" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="C124" s="17" t="s">
+      <c r="C124" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8"/>
       <c r="F124" s="10">
         <v>2</v>
       </c>
@@ -5636,13 +5637,13 @@
       <c r="B125" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="C125" s="17" t="s">
+      <c r="C125" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D125" s="17" t="s">
+      <c r="D125" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="E125" s="17" t="s">
+      <c r="E125" s="16" t="s">
         <v>455</v>
       </c>
       <c r="F125" s="10">
@@ -5656,13 +5657,13 @@
       <c r="B126" s="17" t="s">
         <v>457</v>
       </c>
-      <c r="C126" s="17" t="s">
+      <c r="C126" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D126" s="17" t="s">
+      <c r="D126" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="E126" s="17" t="s">
+      <c r="E126" s="16" t="s">
         <v>459</v>
       </c>
       <c r="F126" s="10">
@@ -5676,11 +5677,11 @@
       <c r="B127" s="17" t="s">
         <v>461</v>
       </c>
-      <c r="C127" s="17" t="s">
+      <c r="C127" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
       <c r="F127" s="10">
         <v>1</v>
       </c>
@@ -5692,11 +5693,11 @@
       <c r="B128" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="C128" s="17" t="s">
+      <c r="C128" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8"/>
       <c r="F128" s="10">
         <v>1</v>
       </c>
@@ -5708,11 +5709,11 @@
       <c r="B129" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="C129" s="17" t="s">
+      <c r="C129" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
+      <c r="D129" s="8"/>
+      <c r="E129" s="8"/>
       <c r="F129" s="10">
         <v>7</v>
       </c>
@@ -5724,11 +5725,11 @@
       <c r="B130" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="C130" s="17" t="s">
+      <c r="C130" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
+      <c r="D130" s="8"/>
+      <c r="E130" s="8"/>
       <c r="F130" s="10">
         <v>1</v>
       </c>
@@ -5740,11 +5741,11 @@
       <c r="B131" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="C131" s="17" t="s">
+      <c r="C131" s="16" t="s">
         <v>470</v>
       </c>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
       <c r="F131" s="10">
         <v>3</v>
       </c>
@@ -5756,11 +5757,11 @@
       <c r="B132" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="C132" s="17" t="s">
+      <c r="C132" s="16" t="s">
         <v>470</v>
       </c>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8"/>
       <c r="F132" s="10">
         <v>2</v>
       </c>
@@ -5772,11 +5773,11 @@
       <c r="B133" s="17" t="s">
         <v>474</v>
       </c>
-      <c r="C133" s="17" t="s">
+      <c r="C133" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
+      <c r="D133" s="8"/>
+      <c r="E133" s="8"/>
       <c r="F133" s="10">
         <v>2</v>
       </c>
@@ -5788,11 +5789,11 @@
       <c r="B134" s="17" t="s">
         <v>476</v>
       </c>
-      <c r="C134" s="17" t="s">
+      <c r="C134" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
+      <c r="D134" s="8"/>
+      <c r="E134" s="8"/>
       <c r="F134" s="10">
         <v>2</v>
       </c>
@@ -5804,11 +5805,11 @@
       <c r="B135" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="C135" s="17" t="s">
+      <c r="C135" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
+      <c r="D135" s="8"/>
+      <c r="E135" s="8"/>
       <c r="F135" s="10">
         <v>2</v>
       </c>
@@ -5820,11 +5821,11 @@
       <c r="B136" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="C136" s="17" t="s">
+      <c r="C136" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
+      <c r="D136" s="8"/>
+      <c r="E136" s="8"/>
       <c r="F136" s="10">
         <v>2</v>
       </c>
@@ -5836,11 +5837,11 @@
       <c r="B137" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="C137" s="17" t="s">
+      <c r="C137" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
+      <c r="D137" s="8"/>
+      <c r="E137" s="8"/>
       <c r="F137" s="10">
         <v>2</v>
       </c>
@@ -5852,13 +5853,13 @@
       <c r="B138" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="C138" s="17" t="s">
+      <c r="C138" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D138" s="17" t="s">
+      <c r="D138" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="E138" s="17" t="s">
+      <c r="E138" s="16" t="s">
         <v>486</v>
       </c>
       <c r="F138" s="10">
@@ -5872,11 +5873,11 @@
       <c r="B139" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="C139" s="17" t="s">
+      <c r="C139" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
+      <c r="D139" s="8"/>
+      <c r="E139" s="8"/>
       <c r="F139" s="10">
         <v>1</v>
       </c>
@@ -5888,11 +5889,11 @@
       <c r="B140" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="C140" s="17" t="s">
+      <c r="C140" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
       <c r="F140" s="10">
         <v>2</v>
       </c>
@@ -5904,11 +5905,11 @@
       <c r="B141" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="C141" s="17" t="s">
+      <c r="C141" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
+      <c r="D141" s="8"/>
+      <c r="E141" s="8"/>
       <c r="F141" s="10">
         <v>1</v>
       </c>
@@ -5920,13 +5921,13 @@
       <c r="B142" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="C142" s="17" t="s">
+      <c r="C142" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D142" s="9"/>
-      <c r="E142" s="17" t="s">
+      <c r="D142" s="16" t="s">
         <v>495</v>
       </c>
+      <c r="E142" s="8"/>
       <c r="F142" s="10">
         <v>1</v>
       </c>
@@ -5938,13 +5939,13 @@
       <c r="B143" s="17" t="s">
         <v>497</v>
       </c>
-      <c r="C143" s="17" t="s">
+      <c r="C143" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="D143" s="17" t="s">
+      <c r="D143" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="E143" s="17" t="s">
+      <c r="E143" s="16" t="s">
         <v>500</v>
       </c>
       <c r="F143" s="10">
@@ -5958,31 +5959,31 @@
       <c r="B144" s="17" t="s">
         <v>502</v>
       </c>
-      <c r="C144" s="17" t="s">
+      <c r="C144" s="16" t="s">
         <v>503</v>
       </c>
-      <c r="D144" s="9"/>
-      <c r="E144" s="17" t="s">
+      <c r="D144" s="16" t="s">
         <v>504</v>
       </c>
+      <c r="E144" s="8"/>
       <c r="F144" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="16" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>505</v>
-      </c>
-      <c r="C145" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="C145" s="16" t="s">
         <v>506</v>
       </c>
-      <c r="D145" s="17" t="s">
+      <c r="D145" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="E145" s="17" t="s">
+      <c r="E145" s="16" t="s">
         <v>508</v>
       </c>
       <c r="F145" s="10">
@@ -5996,13 +5997,13 @@
       <c r="B146" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="C146" s="17" t="s">
+      <c r="C146" s="16" t="s">
         <v>511</v>
       </c>
-      <c r="D146" s="17" t="s">
+      <c r="D146" s="16" t="s">
         <v>512</v>
       </c>
-      <c r="E146" s="17" t="s">
+      <c r="E146" s="16" t="s">
         <v>513</v>
       </c>
       <c r="F146" s="10">
@@ -6016,13 +6017,13 @@
       <c r="B147" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="C147" s="17" t="s">
+      <c r="C147" s="16" t="s">
         <v>516</v>
       </c>
-      <c r="D147" s="17" t="s">
+      <c r="D147" s="16" t="s">
         <v>517</v>
       </c>
-      <c r="E147" s="17" t="s">
+      <c r="E147" s="16" t="s">
         <v>518</v>
       </c>
       <c r="F147" s="10">
@@ -6036,11 +6037,11 @@
       <c r="B148" s="17" t="s">
         <v>520</v>
       </c>
-      <c r="C148" s="17" t="s">
+      <c r="C148" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="8"/>
       <c r="F148" s="10">
         <v>1</v>
       </c>
@@ -6052,25 +6053,25 @@
       <c r="B149" s="17" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="17" t="s">
+      <c r="C149" s="16" t="s">
         <v>524</v>
       </c>
-      <c r="D149" s="9"/>
-      <c r="E149" s="9"/>
+      <c r="D149" s="8"/>
+      <c r="E149" s="8"/>
       <c r="F149" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:6">
-      <c r="A150" s="8"/>
-      <c r="B150" s="17" t="s">
+      <c r="A150" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="C150" s="17" t="s">
+      <c r="B150" s="9"/>
+      <c r="C150" s="16" t="s">
         <v>526</v>
       </c>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
+      <c r="D150" s="8"/>
+      <c r="E150" s="8"/>
       <c r="F150" s="10">
         <v>1</v>
       </c>
@@ -6082,11 +6083,11 @@
       <c r="B151" s="17" t="s">
         <v>528</v>
       </c>
-      <c r="C151" s="17" t="s">
+      <c r="C151" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="D151" s="9"/>
-      <c r="E151" s="9"/>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8"/>
       <c r="F151" s="10">
         <v>1</v>
       </c>
@@ -6098,13 +6099,13 @@
       <c r="B152" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="C152" s="17" t="s">
+      <c r="C152" s="16" t="s">
         <v>532</v>
       </c>
-      <c r="D152" s="17" t="s">
+      <c r="D152" s="16" t="s">
         <v>533</v>
       </c>
-      <c r="E152" s="17" t="s">
+      <c r="E152" s="16" t="s">
         <v>534</v>
       </c>
       <c r="F152" s="10">
@@ -6118,13 +6119,13 @@
       <c r="B153" s="17" t="s">
         <v>536</v>
       </c>
-      <c r="C153" s="17" t="s">
+      <c r="C153" s="16" t="s">
         <v>537</v>
       </c>
-      <c r="D153" s="17" t="s">
+      <c r="D153" s="16" t="s">
         <v>538</v>
       </c>
-      <c r="E153" s="17" t="s">
+      <c r="E153" s="16" t="s">
         <v>539</v>
       </c>
       <c r="F153" s="10">
@@ -6138,13 +6139,13 @@
       <c r="B154" s="17" t="s">
         <v>541</v>
       </c>
-      <c r="C154" s="17" t="s">
+      <c r="C154" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="D154" s="17" t="s">
+      <c r="D154" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="E154" s="17" t="s">
+      <c r="E154" s="16" t="s">
         <v>544</v>
       </c>
       <c r="F154" s="10">
@@ -6158,13 +6159,13 @@
       <c r="B155" s="17" t="s">
         <v>546</v>
       </c>
-      <c r="C155" s="17" t="s">
+      <c r="C155" s="16" t="s">
         <v>547</v>
       </c>
-      <c r="D155" s="17" t="s">
+      <c r="D155" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="E155" s="17" t="s">
+      <c r="E155" s="16" t="s">
         <v>549</v>
       </c>
       <c r="F155" s="10">
@@ -6178,13 +6179,13 @@
       <c r="B156" s="17" t="s">
         <v>551</v>
       </c>
-      <c r="C156" s="17" t="s">
+      <c r="C156" s="16" t="s">
         <v>552</v>
       </c>
-      <c r="D156" s="9"/>
-      <c r="E156" s="17" t="s">
-        <v>550</v>
-      </c>
+      <c r="D156" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="E156" s="8"/>
       <c r="F156" s="10">
         <v>2</v>
       </c>
@@ -6196,13 +6197,13 @@
       <c r="B157" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="C157" s="17" t="s">
+      <c r="C157" s="16" t="s">
         <v>555</v>
       </c>
-      <c r="D157" s="17" t="s">
+      <c r="D157" s="16" t="s">
         <v>556</v>
       </c>
-      <c r="E157" s="17" t="s">
+      <c r="E157" s="16" t="s">
         <v>557</v>
       </c>
       <c r="F157" s="10">
@@ -6210,15 +6211,15 @@
       </c>
     </row>
     <row r="158" spans="1:6">
-      <c r="A158" s="8"/>
-      <c r="B158" s="17" t="s">
+      <c r="A158" s="16" t="s">
         <v>558</v>
       </c>
-      <c r="C158" s="17" t="s">
+      <c r="B158" s="9"/>
+      <c r="C158" s="16" t="s">
         <v>552</v>
       </c>
-      <c r="D158" s="9"/>
-      <c r="E158" s="9"/>
+      <c r="D158" s="8"/>
+      <c r="E158" s="8"/>
       <c r="F158" s="10">
         <v>1</v>
       </c>
@@ -6230,13 +6231,13 @@
       <c r="B159" s="17" t="s">
         <v>560</v>
       </c>
-      <c r="C159" s="17" t="s">
+      <c r="C159" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="D159" s="17" t="s">
+      <c r="D159" s="16" t="s">
         <v>561</v>
       </c>
-      <c r="E159" s="17" t="s">
+      <c r="E159" s="16" t="s">
         <v>562</v>
       </c>
       <c r="F159" s="10">
@@ -6250,41 +6251,41 @@
       <c r="B160" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="C160" s="17" t="s">
+      <c r="C160" s="16" t="s">
         <v>565</v>
       </c>
-      <c r="D160" s="9"/>
-      <c r="E160" s="9"/>
+      <c r="D160" s="8"/>
+      <c r="E160" s="8"/>
       <c r="F160" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="16" t="s">
-        <v>501</v>
+        <v>566</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>566</v>
-      </c>
-      <c r="C161" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="C161" s="16" t="s">
         <v>567</v>
       </c>
-      <c r="D161" s="9"/>
-      <c r="E161" s="9"/>
+      <c r="D161" s="8"/>
+      <c r="E161" s="8"/>
       <c r="F161" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:6">
-      <c r="A162" s="8"/>
-      <c r="B162" s="17" t="s">
+      <c r="A162" s="16" t="s">
         <v>568</v>
       </c>
-      <c r="C162" s="17" t="s">
+      <c r="B162" s="9"/>
+      <c r="C162" s="16" t="s">
         <v>569</v>
       </c>
-      <c r="D162" s="9"/>
-      <c r="E162" s="9"/>
+      <c r="D162" s="8"/>
+      <c r="E162" s="8"/>
       <c r="F162" s="10">
         <v>1</v>
       </c>
@@ -6296,13 +6297,13 @@
       <c r="B163" s="17" t="s">
         <v>571</v>
       </c>
-      <c r="C163" s="17" t="s">
+      <c r="C163" s="16" t="s">
         <v>572</v>
       </c>
-      <c r="D163" s="17" t="s">
+      <c r="D163" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="E163" s="17" t="s">
+      <c r="E163" s="16" t="s">
         <v>574</v>
       </c>
       <c r="F163" s="10">
@@ -6316,13 +6317,13 @@
       <c r="B164" s="17" t="s">
         <v>576</v>
       </c>
-      <c r="C164" s="17" t="s">
+      <c r="C164" s="16" t="s">
         <v>577</v>
       </c>
-      <c r="D164" s="17" t="s">
+      <c r="D164" s="16" t="s">
         <v>578</v>
       </c>
-      <c r="E164" s="17" t="s">
+      <c r="E164" s="16" t="s">
         <v>579</v>
       </c>
       <c r="F164" s="10">
@@ -6336,11 +6337,11 @@
       <c r="B165" s="17" t="s">
         <v>581</v>
       </c>
-      <c r="C165" s="17" t="s">
+      <c r="C165" s="16" t="s">
         <v>582</v>
       </c>
-      <c r="D165" s="9"/>
-      <c r="E165" s="9"/>
+      <c r="D165" s="8"/>
+      <c r="E165" s="8"/>
       <c r="F165" s="10">
         <v>1</v>
       </c>
@@ -6352,13 +6353,13 @@
       <c r="B166" s="17" t="s">
         <v>584</v>
       </c>
-      <c r="C166" s="17" t="s">
+      <c r="C166" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="D166" s="17" t="s">
+      <c r="D166" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="E166" s="17" t="s">
+      <c r="E166" s="16" t="s">
         <v>587</v>
       </c>
       <c r="F166" s="10">
@@ -6372,13 +6373,13 @@
       <c r="B167" s="17" t="s">
         <v>589</v>
       </c>
-      <c r="C167" s="17" t="s">
+      <c r="C167" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="D167" s="17" t="s">
+      <c r="D167" s="16" t="s">
         <v>590</v>
       </c>
-      <c r="E167" s="17" t="s">
+      <c r="E167" s="16" t="s">
         <v>591</v>
       </c>
       <c r="F167" s="10">
@@ -6392,11 +6393,11 @@
       <c r="B168" s="17" t="s">
         <v>593</v>
       </c>
-      <c r="C168" s="17" t="s">
+      <c r="C168" s="16" t="s">
         <v>594</v>
       </c>
-      <c r="D168" s="9"/>
-      <c r="E168" s="9"/>
+      <c r="D168" s="8"/>
+      <c r="E168" s="8"/>
       <c r="F168" s="10">
         <v>1</v>
       </c>
@@ -6408,13 +6409,13 @@
       <c r="B169" s="17" t="s">
         <v>596</v>
       </c>
-      <c r="C169" s="17" t="s">
+      <c r="C169" s="16" t="s">
         <v>597</v>
       </c>
-      <c r="D169" s="17" t="s">
+      <c r="D169" s="16" t="s">
         <v>598</v>
       </c>
-      <c r="E169" s="17" t="s">
+      <c r="E169" s="16" t="s">
         <v>599</v>
       </c>
       <c r="F169" s="10">
@@ -6428,13 +6429,13 @@
       <c r="B170" s="19" t="s">
         <v>601</v>
       </c>
-      <c r="C170" s="19" t="s">
+      <c r="C170" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="D170" s="19" t="s">
+      <c r="D170" s="18" t="s">
         <v>602</v>
       </c>
-      <c r="E170" s="19" t="s">
+      <c r="E170" s="18" t="s">
         <v>603</v>
       </c>
       <c r="F170" s="13">
